--- a/astro-site/public/dl/bar-checklist-templates/04-bartender-checklist-duties-by-role.xlsx
+++ b/astro-site/public/dl/bar-checklist-templates/04-bartender-checklist-duties-by-role.xlsx
@@ -1816,7 +1816,7 @@
       </c>
       <c r="B13" s="40" t="inlineStr">
         <is>
-          <t>Make cocktails from the menu and special orders</t>
+          <t>Make cocktails from the menu and special orders; card guests per house policy (21+) and never serve anyone visibly intoxicated</t>
         </is>
       </c>
       <c r="C13" s="41" t="inlineStr">
@@ -2369,7 +2369,7 @@
       </c>
       <c r="B9" s="40" t="inlineStr">
         <is>
-          <t>Wash glassware in the glass washer</t>
+          <t>Wash glassware in the glass washer; test the sanitizer with strips at the start of the shift (ppm on the label)</t>
         </is>
       </c>
       <c r="C9" s="41" t="inlineStr">
@@ -2894,7 +2894,7 @@
       </c>
       <c r="B7" s="40" t="inlineStr">
         <is>
-          <t>Take orders with knowledge of the cocktail menu</t>
+          <t>Take orders with knowledge of the cocktail menu; card guests per house policy (21+) and stop serving anyone visibly intoxicated</t>
         </is>
       </c>
       <c r="C7" s="41" t="inlineStr">
